--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
+++ b/ci-build/StructureDefinition-senologie-bildgebung-sonstige.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$41</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="381">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: BildgebungSonstige</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -1532,7 +1538,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN41"/>
+  <dimension ref="A1:AP41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.671875" customWidth="true" bestFit="true"/>
@@ -1570,10 +1576,12 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="147.17578125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="104.53515625" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="39.32421875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="147.17578125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="104.53515625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1697,6 +1705,12 @@
       <c r="AN1" t="s" s="1">
         <v>76</v>
       </c>
+      <c r="AO1" t="s" s="1">
+        <v>77</v>
+      </c>
+      <c r="AP1" t="s" s="1">
+        <v>78</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1707,14 +1721,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1726,16 +1740,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1788,36 +1802,42 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AO2" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AP2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1825,10 +1845,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1837,19 +1857,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1899,13 +1919,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1923,15 +1943,21 @@
         <v>20</v>
       </c>
       <c r="AN3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1939,10 +1965,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1951,16 +1977,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2011,19 +2037,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -2035,15 +2061,21 @@
         <v>20</v>
       </c>
       <c r="AN4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2051,31 +2083,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2125,19 +2157,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -2149,15 +2181,21 @@
         <v>20</v>
       </c>
       <c r="AN5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2165,10 +2203,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2180,16 +2218,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2215,13 +2253,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -2239,19 +2277,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -2263,26 +2301,32 @@
         <v>20</v>
       </c>
       <c r="AN6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -2294,16 +2338,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2353,19 +2397,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2374,29 +2418,35 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2408,16 +2458,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2467,13 +2517,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2488,18 +2538,24 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2507,10 +2563,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2522,13 +2578,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2567,29 +2623,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2601,28 +2657,34 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -2634,13 +2696,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2691,19 +2753,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2715,50 +2777,56 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2807,19 +2875,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2828,29 +2896,35 @@
         <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2859,22 +2933,22 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2923,50 +2997,56 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>20</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>164</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AP12" t="s" s="2">
+        <v>166</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2978,19 +3058,19 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3039,39 +3119,45 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3079,145 +3165,151 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y14" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="S14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y14" t="s" s="2">
+      <c r="Z14" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="Z14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>175</v>
-      </c>
       <c r="AG14" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>182</v>
+        <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>184</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>185</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AP14" t="s" s="2">
+        <v>187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3228,7 +3320,7 @@
         <v>20</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>20</v>
@@ -3243,13 +3335,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -3267,71 +3359,77 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>196</v>
+        <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>197</v>
+        <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>198</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3357,13 +3455,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -3381,39 +3479,45 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>209</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>211</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3421,10 +3525,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3436,13 +3540,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3493,13 +3597,13 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
@@ -3514,29 +3618,35 @@
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3548,16 +3658,16 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3595,31 +3705,31 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3628,18 +3738,24 @@
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3647,34 +3763,34 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3711,86 +3827,92 @@
         <v>20</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AC19" s="2"/>
       <c r="AD19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3800,7 +3922,7 @@
         <v>20</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>20</v>
@@ -3839,76 +3961,82 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3918,7 +4046,7 @@
         <v>20</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>20</v>
@@ -3957,39 +4085,45 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3997,10 +4131,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4009,22 +4143,22 @@
         <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4073,72 +4207,78 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>245</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>246</v>
+        <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4187,50 +4327,56 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>253</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>254</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>255</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>256</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>258</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -4239,22 +4385,22 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4303,50 +4449,56 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>265</v>
+        <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>267</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>269</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -4355,22 +4507,22 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4407,86 +4559,92 @@
         <v>20</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>278</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>279</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AP25" t="s" s="2">
+        <v>281</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4535,50 +4693,56 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>277</v>
+        <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>278</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>279</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>281</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4587,22 +4751,22 @@
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4651,50 +4815,56 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>291</v>
+        <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>292</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>293</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>295</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4703,22 +4873,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4767,74 +4937,80 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>302</v>
+        <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>303</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>304</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>306</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4883,39 +5059,45 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>301</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>303</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>306</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4923,10 +5105,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -4938,19 +5120,19 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -4999,53 +5181,59 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>317</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>255</v>
+        <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>20</v>
@@ -5054,19 +5242,19 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5115,39 +5303,45 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>325</v>
+        <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5155,10 +5349,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5170,16 +5364,16 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5229,19 +5423,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5250,29 +5444,35 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>332</v>
+        <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -5281,20 +5481,20 @@
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5343,39 +5543,45 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>326</v>
+        <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5383,10 +5589,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5398,13 +5604,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5455,13 +5661,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5476,29 +5682,35 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5510,16 +5722,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5569,19 +5781,19 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>20</v>
@@ -5590,53 +5802,59 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5685,19 +5903,19 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
@@ -5706,18 +5924,24 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5725,10 +5949,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5740,19 +5964,19 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5801,19 +6025,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -5822,18 +6046,24 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5841,10 +6071,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5853,16 +6083,16 @@
         <v>20</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5913,19 +6143,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -5934,32 +6164,38 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>357</v>
+        <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -5968,17 +6204,17 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6027,39 +6263,45 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>364</v>
+        <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AP39" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6067,13 +6309,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
@@ -6082,16 +6324,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6117,13 +6359,13 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>20</v>
@@ -6141,39 +6383,45 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6181,10 +6429,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6196,19 +6444,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6257,35 +6505,41 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN41">
+  <autoFilter ref="A1:AP41">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
